--- a/results/辽宁省.xlsx
+++ b/results/辽宁省.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="128">
   <si>
     <t>车站</t>
   </si>
@@ -389,6 +389,12 @@
   </si>
   <si>
     <t>D506</t>
+  </si>
+  <si>
+    <t>D7603  G8172  D7607  G9122  G8176  G704  G8088  G706  D7615  G8180  G9128  G2649  G720  D7683  G9130  D7669  G1229  G787  G153  G8026</t>
+  </si>
+  <si>
+    <t>G8172  D7607  G9122  G8176  G704  G8088  G706  C1153  D7615</t>
   </si>
 </sst>
 </file>
@@ -765,7 +771,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F88"/>
+  <dimension ref="A1:F89"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="3" width="15" customWidth="1"/>
@@ -2532,6 +2538,26 @@
         <v>13</v>
       </c>
     </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>11</v>
+      </c>
+      <c r="B89" t="s">
+        <v>7</v>
+      </c>
+      <c r="C89" t="s">
+        <v>8</v>
+      </c>
+      <c r="D89" t="s">
+        <v>126</v>
+      </c>
+      <c r="E89" t="s">
+        <v>10</v>
+      </c>
+      <c r="F89" t="s">
+        <v>127</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
